--- a/rbda-kiosk/du_lieu_test/TEST_01_danh_sach_CLB.xlsx
+++ b/rbda-kiosk/du_lieu_test/TEST_01_danh_sach_CLB.xlsx
@@ -471,100 +471,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CLB Bóng rổ</t>
+          <t>CLB Bóng đá</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>chinh_sach</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLB Bóng đá</t>
+          <t>CLB Tin học</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>chinh_sach</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLB Tiếng Anh</t>
+          <t>CLB Mỹ thuật</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>chinh_sach</t>
+          <t>khoi_10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLB Tin học</t>
+          <t>CLB Bóng rổ</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>chinh_sach</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CLB Robotics</t>
+          <t>CLB Âm nhạc</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -574,58 +578,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CLB Âm nhạc</t>
+          <t>CLB Tiếng Anh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>khoi_10</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_robotics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CLB Mỹ thuật</t>
+          <t>CLB Robotics</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>khoi_10</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_khoahoc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CLB Văn học</t>
+          <t>CLB Khoa học</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -635,25 +639,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLB Khoa học</t>
+          <t>CLB Văn học</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>khoi_10</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -714,46 +714,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ba CLB có suất dự trữ: Tiếng Anh và Tin học dành cho nhóm</t>
+          <t>Bốn CLB có suất dự trữ, và ĐỀU là CLB đông người đăng ký:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chinh_sach; Mỹ thuật và Khoa học dành cho nhóm khoi_10.</t>
+          <t>Bóng đá và Tin học dành cho nhóm chinh_sach; Mỹ thuật và Tiếng</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Anh dành cho nhóm khoi_10. Đặt suất dự trữ ở CLB còn thừa chỗ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>thì suất đó vô dụng, vì ai cũng vào được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>NHẬP FILE NÀY TRƯỚC hai file học sinh — nếu không, mọi học sinh</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sẽ bị bỏ qua vì mã CLB chưa tồn tại.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>sẽ bị bỏ qua vì mã CLB chưa tồn tại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Sinh bằng du_lieu_test/tao_du_lieu_test.py, seed = 2026</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Chạy lại script luôn cho ra đúng bộ dữ liệu này.</t>
         </is>
